--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46155</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44852</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45463</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45174</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45281</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45337</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44634</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45281</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>44678</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46155</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45988</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45617</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45942</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44607</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44865</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44739</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45232</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45692</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45645</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>45897</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45751</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45107</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44901</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45988</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45988</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44935</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45264</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45638</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>46232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44711</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44525</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44601</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44733</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44691</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44698</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44540</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44636</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44880</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44551</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44722</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44571</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44608</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44676</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44662</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44572</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44623</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44761</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44847</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44826</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45180</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45232</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>44637</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45110</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44739</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44559</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44610</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44610</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45019</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45639</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44961</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45072</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45705</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45370</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45223</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>45628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45019</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45638</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45453</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>45506</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44875</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44977</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>44987</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44999</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>45279</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45456</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>44635</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>45251</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>45125</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>45279</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44648</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44645</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45219</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44635</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44635</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>44908</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45174</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45027</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45027</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44825</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>46136</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45908</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45607</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44999</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45908</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45219</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44958</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>44582</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45926</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>44600</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45414</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45279</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45945</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45945</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45947</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45553</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45160</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44659</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44595</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>46154</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45979</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44509</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45077</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44914</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45761</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45042</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46162</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44717</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45219</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>46163</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44680</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46169</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45110</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>46169</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44636</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45628</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45443</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45274</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44986</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44899</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>46169</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45019</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>46170</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>46030</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44636</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44636</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>44840</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44574</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44893</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44664</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45110</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45019</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45019</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45042</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44900</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>46059</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45761</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>46062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45083</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45400</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44606</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45735</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>46184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46079</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>46183</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>46084</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>46084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>46078</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44523</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>46083</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>46188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>45579</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44901</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46188</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45218</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>46190</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45264</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45042</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>46196</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45457</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>46104</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46195</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45553</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>46112</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>46112</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>46112</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>46112</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>46112</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>44523</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44623</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46120</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>46121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45033</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44556</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44498</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45603</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46135</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>44792</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45222</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44874</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44708</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>44755</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44523</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45169</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>44482</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45705</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45713</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44658</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>44903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>46080</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>46080</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45028</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45398</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45603</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45366</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46213</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>46215</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>46215</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46215</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44537</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>46215</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46215</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46215</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45282</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45296</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45037</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46184</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45223</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46217</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>44552</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45153</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>46265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45448</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46154</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44657</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>46066</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45378</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>46066</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>46272</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>46274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>46274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>46265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45506</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45545</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45798</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45235</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45603</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45617</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45833</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45516</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>44880</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>44880</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45833</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45833</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>43948</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44740</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45005</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>44634</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>46091</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46113</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>46134</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44523</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44871</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44852</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>46155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45203</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45740</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45337</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45279</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44634</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45281</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>44678</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45988</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>45617</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46155</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44764</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45942</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44607</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>45232</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44641</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45751</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>45107</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45645</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45988</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45001</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>46154</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>44901</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45638</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>45196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>46232</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>46290</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>46290</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44865</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45692</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45264</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45414</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45453</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45296</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45456</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44816</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>44986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>44903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>44482</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45083</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44874</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45019</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>45545</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45279</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>45506</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45042</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45798</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45595</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44875</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44899</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45366</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45908</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44914</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44936</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44636</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>46079</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45952</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>46084</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>46083</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45235</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44999</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44977</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44717</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44662</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>46104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45953</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44509</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>46112</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>46112</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>46112</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>46112</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>46121</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>46120</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45639</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45628</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45027</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44999</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>46135</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44582</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45929</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46136</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45617</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45705</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44840</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>44893</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>46154</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44874</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45223</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>46154</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44900</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45833</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45110</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45222</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>46162</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>46163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45516</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44880</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44880</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45833</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>44552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46169</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45274</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45119</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44812</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45457</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45532</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>46170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>44559</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44595</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45218</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44637</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45028</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>46183</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>46188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>44978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>46188</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45174</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>46190</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>46195</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45042</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44556</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45628</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>44645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45506</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44523</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45832</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>44636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44606</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45169</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44623</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>44658</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46080</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44635</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44610</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>46080</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44635</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44708</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45705</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>46215</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>46215</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>46213</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>46215</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46215</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>46215</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>46215</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45180</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44680</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44743</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45219</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44664</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46184</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45219</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44722</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44739</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>46154</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45279</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45282</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46265</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44847</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46066</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44961</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>46274</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46274</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>44523</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>44671</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45448</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44657</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44755</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44987</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44610</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>46272</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45443</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45553</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45579</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44600</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46289</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46289</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45110</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45603</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44498</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44659</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44574</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45603</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45398</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45110</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45232</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45019</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45042</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45033</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45370</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45019</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45713</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45638</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45264</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45162</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45378</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>43948</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44634</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46091</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44523</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44871</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44852</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>46155</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45203</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14265-2025</t>
+          <t>A 59143-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45740</v>
+        <v>45988</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3435,20 +3435,25 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3460,834 +3465,830 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Järpe
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59143-2025 artfynd.xlsx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59143-2025 karta.png", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59143-2025 georefererad karta.tif", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59143-2025 FSC-klagomål.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59143-2025 FSC-klagomål mail.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59143-2025 tillsynsbegäran.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59143-2025 tillsynsbegäran mail.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59143-2025 prioriterade fågelarter.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 14265-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45740</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 14265-2025 artfynd.xlsx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 14265-2025 karta.png", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 14265-2025 georefererad karta.tif", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="Z26">
+      <c r="Z27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/knärot/A 14265-2025 karta knärot.png", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 14265-2025 FSC-klagomål.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 14265-2025 FSC-klagomål mail.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 14265-2025 tillsynsbegäran.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 14265-2025 tillsynsbegäran mail.docx", "A 14265-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 6249-2024</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>6.5</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S28" t="n">
         <v>3</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Blåsippa
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 6249-2024 artfynd.xlsx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 6249-2024 karta.png", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 6249-2024 georefererad karta.tif", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 6249-2024 FSC-klagomål.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 6249-2024 FSC-klagomål mail.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 6249-2024 tillsynsbegäran.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 6249-2024 tillsynsbegäran mail.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 6249-2024 prioriterade fågelarter.docx", "A 6249-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 64735-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>12.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>3</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Vårstarr
 Gullviva</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 64735-2023 artfynd.xlsx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 64735-2023 karta.png", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 64735-2023 georefererad karta.tif", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 64735-2023 FSC-klagomål.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 64735-2023 FSC-klagomål mail.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 64735-2023 tillsynsbegäran.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 64735-2023 tillsynsbegäran mail.docx", "A 64735-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 64201-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>45279</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>13</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Källpraktmossa
 Stubbspretmossa
 Vanlig rörsvepemossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 64201-2023 artfynd.xlsx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 64201-2023 karta.png", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 64201-2023 georefererad karta.tif", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 64201-2023 FSC-klagomål.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 64201-2023 FSC-klagomål mail.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 64201-2023 tillsynsbegäran.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 64201-2023 tillsynsbegäran mail.docx", "A 64201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 11804-2022</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>44634</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>10.6</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>3</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Ask
 Svart trolldruva
 Nattviol</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 11804-2022 artfynd.xlsx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 11804-2022 karta.png", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 11804-2022 georefererad karta.tif", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 11804-2022 FSC-klagomål.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 11804-2022 FSC-klagomål mail.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 11804-2022 tillsynsbegäran.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 11804-2022 tillsynsbegäran mail.docx", "A 11804-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>S 4578-2023</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>4.1</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Vårstarr
 Gullviva</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/S 4578-2023 artfynd.xlsx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/S 4578-2023 karta.png", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/S 4578-2023 georefererad karta.tif", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/S 4578-2023 FSC-klagomål.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/S 4578-2023 FSC-klagomål mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/S 4578-2023 tillsynsbegäran.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/S 4578-2023 tillsynsbegäran mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 17261-2022</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>44678</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>1.1</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>2</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Skumticka
 Svartöra</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 17261-2022 artfynd.xlsx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 17261-2022 karta.png", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 17261-2022 georefererad karta.tif", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 17261-2022 FSC-klagomål.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 17261-2022 FSC-klagomål mail.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 17261-2022 tillsynsbegäran.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 17261-2022 tillsynsbegäran mail.docx", "A 17261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 59143-2025</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59143-2025 artfynd.xlsx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59143-2025 karta.png", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59143-2025 georefererad karta.tif", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59143-2025 FSC-klagomål.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59143-2025 FSC-klagomål mail.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59143-2025 tillsynsbegäran.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59143-2025 tillsynsbegäran mail.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59143-2025 prioriterade fågelarter.docx", "A 59143-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9327-2026</t>
+          <t>A 59140-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4301,10 +4302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46070</v>
+        <v>45988</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4318,17 +4319,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4358,696 +4359,702 @@
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59140-2025 artfynd.xlsx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59140-2025 karta.png", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59140-2025 georefererad karta.tif", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59140-2025 FSC-klagomål.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59140-2025 FSC-klagomål mail.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59140-2025 tillsynsbegäran.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59140-2025 tillsynsbegäran mail.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59140-2025 prioriterade fågelarter.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 9327-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Tibast</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 9327-2026 artfynd.xlsx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 9327-2026 karta.png", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 9327-2026 georefererad karta.tif", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 9327-2026 FSC-klagomål.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 9327-2026 FSC-klagomål mail.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 9327-2026 tillsynsbegäran.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 9327-2026 tillsynsbegäran mail.docx", "A 9327-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 54536-2024</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>45617</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="E36" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>4</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>4</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>2</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Svinrot</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 54536-2024 artfynd.xlsx", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 54536-2024 karta.png", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 54536-2024 georefererad karta.tif", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 54536-2024 FSC-klagomål.docx", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 54536-2024 FSC-klagomål mail.docx", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 54536-2024 tillsynsbegäran.docx", "A 54536-2024")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 54536-2024 tillsynsbegäran mail.docx", "A 54536-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 22452-2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="E37" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>4</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>2</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>2</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Kopparödla</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 22452-2026 artfynd.xlsx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 22452-2026 karta.png", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 22452-2026 georefererad karta.tif", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 22452-2026 FSC-klagomål.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 22452-2026 FSC-klagomål mail.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 22452-2026 tillsynsbegäran.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 22452-2026 tillsynsbegäran mail.docx", "A 22452-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 59566-2021</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>44491</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="E38" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>2.1</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>4</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Vanlig flatbagge</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59566-2021 artfynd.xlsx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59566-2021 karta.png", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59566-2021 georefererad karta.tif", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59566-2021 FSC-klagomål.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59566-2021 FSC-klagomål mail.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59566-2021 tillsynsbegäran.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59566-2021 tillsynsbegäran mail.docx", "A 59566-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 30759-2022</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>44764</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="E39" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I39" t="n">
         <v>0.8</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>2</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>5</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>4</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Blåsippa</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 30759-2022 artfynd.xlsx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 30759-2022 karta.png", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 30759-2022 georefererad karta.tif", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 30759-2022 FSC-klagomål.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 30759-2022 FSC-klagomål mail.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 30759-2022 tillsynsbegäran.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 30759-2022 tillsynsbegäran mail.docx", "A 30759-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>S 2846-2025</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D40" s="1" t="n">
         <v>45942</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
+      <c r="E40" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>3.7</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>2</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>2</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T40" t="n">
         <v>2</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Svart trolldruva</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/S 2846-2025 artfynd.xlsx", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/S 2846-2025 karta.png", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/S 2846-2025 georefererad karta.tif", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/S 2846-2025 FSC-klagomål.docx", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/S 2846-2025 FSC-klagomål mail.docx", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/S 2846-2025 tillsynsbegäran.docx", "S 2846-2025")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/S 2846-2025 tillsynsbegäran mail.docx", "S 2846-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A 30761-2022</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>44764</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>Nötkråka</t>
-        </is>
-      </c>
-      <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 30761-2022 artfynd.xlsx", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 30761-2022 karta.png", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 30761-2022 georefererad karta.tif", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 30761-2022 FSC-klagomål.docx", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 30761-2022 FSC-klagomål mail.docx", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 30761-2022 tillsynsbegäran.docx", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 30761-2022 tillsynsbegäran mail.docx", "A 30761-2022")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 30761-2022 prioriterade fågelarter.docx", "A 30761-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7534-2022</t>
+          <t>A 30761-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5057,14 +5064,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44607</v>
+        <v>44764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5077,7 +5084,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5086,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5101,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5117,42 +5124,46 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 7534-2022 artfynd.xlsx", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 30761-2022 artfynd.xlsx", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 7534-2022 karta.png", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 30761-2022 karta.png", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 7534-2022 georefererad karta.tif", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 30761-2022 georefererad karta.tif", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 7534-2022 FSC-klagomål.docx", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 30761-2022 FSC-klagomål.docx", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 7534-2022 FSC-klagomål mail.docx", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 30761-2022 FSC-klagomål mail.docx", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 7534-2022 tillsynsbegäran.docx", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 30761-2022 tillsynsbegäran.docx", "A 30761-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 7534-2022 tillsynsbegäran mail.docx", "A 7534-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 30761-2022 tillsynsbegäran mail.docx", "A 30761-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 30761-2022 prioriterade fågelarter.docx", "A 30761-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55676-2023</t>
+          <t>A 7534-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5166,10 +5177,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45232</v>
+        <v>44607</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,13 +5192,8 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>37.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5227,46 +5233,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 55676-2023 artfynd.xlsx", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 7534-2022 artfynd.xlsx", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 55676-2023 karta.png", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 7534-2022 karta.png", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 55676-2023 georefererad karta.tif", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 7534-2022 georefererad karta.tif", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 55676-2023 FSC-klagomål.docx", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 7534-2022 FSC-klagomål.docx", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 55676-2023 FSC-klagomål mail.docx", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 7534-2022 FSC-klagomål mail.docx", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 55676-2023 tillsynsbegäran.docx", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 7534-2022 tillsynsbegäran.docx", "A 7534-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 55676-2023 tillsynsbegäran mail.docx", "A 55676-2023")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 55676-2023 prioriterade fågelarter.docx", "A 55676-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 7534-2022 tillsynsbegäran mail.docx", "A 7534-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40886-2025</t>
+          <t>A 55676-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5276,14 +5278,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45897</v>
+        <v>45232</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,14 +5297,19 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>37.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5332,46 +5339,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 40886-2025 artfynd.xlsx", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 55676-2023 artfynd.xlsx", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 40886-2025 karta.png", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 55676-2023 karta.png", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 40886-2025 georefererad karta.tif", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 55676-2023 georefererad karta.tif", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 40886-2025 FSC-klagomål.docx", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 55676-2023 FSC-klagomål.docx", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 40886-2025 FSC-klagomål mail.docx", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 55676-2023 FSC-klagomål mail.docx", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 40886-2025 tillsynsbegäran.docx", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 55676-2023 tillsynsbegäran.docx", "A 55676-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 40886-2025 tillsynsbegäran mail.docx", "A 40886-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 55676-2023 tillsynsbegäran mail.docx", "A 55676-2023")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 55676-2023 prioriterade fågelarter.docx", "A 55676-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12905-2022</t>
+          <t>A 40886-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5385,10 +5396,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44641</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,19 +5411,14 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>23.9</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5421,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5430,10 +5436,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5446,42 +5452,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 12905-2022 artfynd.xlsx", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 40886-2025 artfynd.xlsx", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 12905-2022 karta.png", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 40886-2025 karta.png", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 12905-2022 georefererad karta.tif", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 40886-2025 georefererad karta.tif", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 12905-2022 FSC-klagomål.docx", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 40886-2025 FSC-klagomål.docx", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 12905-2022 FSC-klagomål mail.docx", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 40886-2025 FSC-klagomål mail.docx", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 12905-2022 tillsynsbegäran.docx", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 40886-2025 tillsynsbegäran.docx", "A 40886-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 12905-2022 tillsynsbegäran mail.docx", "A 12905-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 40886-2025 tillsynsbegäran mail.docx", "A 40886-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16374-2025</t>
+          <t>A 12905-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5495,10 +5501,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45751</v>
+        <v>44641</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5510,24 +5516,29 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>23.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -5535,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5547,46 +5558,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 16374-2025 artfynd.xlsx", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 12905-2022 artfynd.xlsx", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 16374-2025 karta.png", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 12905-2022 karta.png", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 16374-2025 georefererad karta.tif", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 12905-2022 georefererad karta.tif", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 16374-2025 FSC-klagomål.docx", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 12905-2022 FSC-klagomål.docx", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 16374-2025 FSC-klagomål mail.docx", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 12905-2022 FSC-klagomål mail.docx", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 16374-2025 tillsynsbegäran.docx", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 12905-2022 tillsynsbegäran.docx", "A 12905-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 16374-2025 tillsynsbegäran mail.docx", "A 16374-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 12905-2022 tillsynsbegäran mail.docx", "A 12905-2022")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29787-2023</t>
+          <t>A 16374-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5600,10 +5611,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45107</v>
+        <v>45751</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5615,19 +5626,14 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5657,46 +5663,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 29787-2023 artfynd.xlsx", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 16374-2025 artfynd.xlsx", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 29787-2023 karta.png", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 16374-2025 karta.png", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 29787-2023 georefererad karta.tif", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 16374-2025 georefererad karta.tif", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 29787-2023 FSC-klagomål.docx", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 16374-2025 FSC-klagomål.docx", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 29787-2023 FSC-klagomål mail.docx", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 16374-2025 FSC-klagomål mail.docx", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 29787-2023 tillsynsbegäran.docx", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 16374-2025 tillsynsbegäran.docx", "A 16374-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 29787-2023 tillsynsbegäran mail.docx", "A 29787-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 16374-2025 tillsynsbegäran mail.docx", "A 16374-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61059-2024</t>
+          <t>A 29787-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5710,10 +5716,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45645</v>
+        <v>45107</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5725,17 +5731,22 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5750,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5766,42 +5777,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Bandad skulderbock</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 61059-2024 artfynd.xlsx", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 29787-2023 artfynd.xlsx", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 61059-2024 karta.png", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 29787-2023 karta.png", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 61059-2024 georefererad karta.tif", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 29787-2023 georefererad karta.tif", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 61059-2024 FSC-klagomål.docx", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 29787-2023 FSC-klagomål.docx", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 61059-2024 FSC-klagomål mail.docx", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 29787-2023 FSC-klagomål mail.docx", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 61059-2024 tillsynsbegäran.docx", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 29787-2023 tillsynsbegäran.docx", "A 29787-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 61059-2024 tillsynsbegäran mail.docx", "A 61059-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 29787-2023 tillsynsbegäran mail.docx", "A 29787-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59144-2025</t>
+          <t>A 61059-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5815,10 +5826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45988</v>
+        <v>45645</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5830,23 +5841,18 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
@@ -5860,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5876,42 +5882,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bandad skulderbock</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59144-2025 artfynd.xlsx", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 61059-2024 artfynd.xlsx", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59144-2025 karta.png", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 61059-2024 karta.png", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59144-2025 georefererad karta.tif", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 61059-2024 georefererad karta.tif", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59144-2025 FSC-klagomål.docx", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 61059-2024 FSC-klagomål.docx", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59144-2025 FSC-klagomål mail.docx", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 61059-2024 FSC-klagomål mail.docx", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59144-2025 tillsynsbegäran.docx", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 61059-2024 tillsynsbegäran.docx", "A 61059-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59144-2025 tillsynsbegäran mail.docx", "A 59144-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 61059-2024 tillsynsbegäran mail.docx", "A 61059-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59140-2025</t>
+          <t>A 59144-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5928,7 +5934,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5946,7 +5952,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -5986,39 +5992,35 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59140-2025 artfynd.xlsx", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59144-2025 artfynd.xlsx", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59140-2025 karta.png", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59144-2025 karta.png", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59140-2025 georefererad karta.tif", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59144-2025 georefererad karta.tif", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59140-2025 FSC-klagomål.docx", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59144-2025 FSC-klagomål.docx", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59140-2025 FSC-klagomål mail.docx", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59144-2025 FSC-klagomål mail.docx", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59140-2025 tillsynsbegäran.docx", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59144-2025 tillsynsbegäran.docx", "A 59144-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59140-2025 tillsynsbegäran mail.docx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59140-2025 prioriterade fågelarter.docx", "A 59140-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59144-2025 tillsynsbegäran mail.docx", "A 59144-2025")</f>
         <v/>
       </c>
     </row>
@@ -6042,7 +6044,7 @@
         <v>45001</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6147,7 +6149,7 @@
         <v>44935</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6258,7 @@
         <v>46154</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6361,7 +6363,7 @@
         <v>44901</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6468,7 @@
         <v>45638</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6571,7 +6573,7 @@
         <v>45196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6676,7 +6678,7 @@
         <v>44610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6786,7 +6788,7 @@
         <v>44739</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6891,7 +6893,7 @@
         <v>45219</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6998,7 @@
         <v>46232</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7108,7 @@
         <v>46290</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7216,7 +7218,7 @@
         <v>46290</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7326,7 +7328,7 @@
         <v>44865</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7431,7 +7433,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7543,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7657,7 @@
         <v>45692</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7762,7 @@
         <v>45264</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7867,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7974,7 +7976,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8047,7 +8049,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8120,7 +8122,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8193,7 +8195,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8266,7 +8268,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8339,7 +8341,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8412,7 +8414,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8485,7 +8487,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8558,7 +8560,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8636,7 +8638,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8709,7 +8711,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8782,7 +8784,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8855,7 +8857,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8933,7 +8935,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9011,7 +9013,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9089,7 +9091,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9162,7 +9164,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9240,7 +9242,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9313,7 +9315,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9386,7 +9388,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9459,7 +9461,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9532,7 +9534,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9605,7 +9607,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9683,7 +9685,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9756,7 +9758,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9829,7 +9831,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9907,7 +9909,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9985,7 +9987,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10058,7 +10060,7 @@
         <v>45042</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10131,7 +10133,7 @@
         <v>45219</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10204,7 +10206,7 @@
         <v>44825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10277,7 +10279,7 @@
         <v>45414</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10350,7 +10352,7 @@
         <v>44792</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10423,7 +10425,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10501,7 +10503,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10574,7 +10576,7 @@
         <v>45453</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10647,7 +10649,7 @@
         <v>45296</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10720,7 +10722,7 @@
         <v>45456</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10793,7 +10795,7 @@
         <v>45223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10866,7 +10868,7 @@
         <v>44816</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10939,7 +10941,7 @@
         <v>44986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11012,7 +11014,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11085,7 +11087,7 @@
         <v>44903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11158,7 +11160,7 @@
         <v>44482</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11231,7 +11233,7 @@
         <v>45083</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11304,7 +11306,7 @@
         <v>44874</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11377,7 +11379,7 @@
         <v>45019</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11450,7 +11452,7 @@
         <v>44908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11523,7 +11525,7 @@
         <v>45545</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11596,7 +11598,7 @@
         <v>45279</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11669,7 +11671,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11747,7 +11749,7 @@
         <v>45506</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11825,7 +11827,7 @@
         <v>45042</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11898,7 +11900,7 @@
         <v>45798</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11971,7 +11973,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12044,7 +12046,7 @@
         <v>45595</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12122,7 +12124,7 @@
         <v>44875</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12195,7 +12197,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12268,7 +12270,7 @@
         <v>44537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12341,7 +12343,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12414,7 +12416,7 @@
         <v>44899</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12487,7 +12489,7 @@
         <v>45366</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12560,7 +12562,7 @@
         <v>45908</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12633,7 +12635,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12706,7 +12708,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12779,7 +12781,7 @@
         <v>44914</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12852,7 +12854,7 @@
         <v>44936</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12925,7 +12927,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12998,7 +13000,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13071,7 +13073,7 @@
         <v>44636</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13149,7 +13151,7 @@
         <v>44636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13227,7 +13229,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13305,7 +13307,7 @@
         <v>46079</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13378,7 +13380,7 @@
         <v>45952</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13456,7 +13458,7 @@
         <v>46084</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13529,7 +13531,7 @@
         <v>46083</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13602,7 +13604,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13675,7 +13677,7 @@
         <v>45235</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13753,7 +13755,7 @@
         <v>45603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13826,7 +13828,7 @@
         <v>44594</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13899,7 +13901,7 @@
         <v>46084</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13972,7 +13974,7 @@
         <v>45037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14050,7 +14052,7 @@
         <v>44999</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14123,7 +14125,7 @@
         <v>44977</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14196,7 +14198,7 @@
         <v>44717</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14269,7 +14271,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14342,7 +14344,7 @@
         <v>44662</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14415,7 +14417,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14488,7 +14490,7 @@
         <v>46104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14561,7 +14563,7 @@
         <v>45947</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14639,7 +14641,7 @@
         <v>45953</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14712,7 +14714,7 @@
         <v>44509</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14785,7 +14787,7 @@
         <v>46112</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14863,7 +14865,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14936,7 +14938,7 @@
         <v>46112</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15009,7 +15011,7 @@
         <v>46112</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15087,7 +15089,7 @@
         <v>46112</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15165,7 +15167,7 @@
         <v>46121</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15243,7 +15245,7 @@
         <v>46120</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15321,7 +15323,7 @@
         <v>45639</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15394,7 +15396,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15467,7 +15469,7 @@
         <v>45628</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15540,7 +15542,7 @@
         <v>45973</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15613,7 +15615,7 @@
         <v>45027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15686,7 +15688,7 @@
         <v>45027</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15759,7 +15761,7 @@
         <v>44826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15832,7 +15834,7 @@
         <v>45979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15905,7 +15907,7 @@
         <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15978,7 +15980,7 @@
         <v>44999</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16051,7 +16053,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16124,7 +16126,7 @@
         <v>46135</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16197,7 +16199,7 @@
         <v>45988</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16275,7 +16277,7 @@
         <v>44582</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16353,7 +16355,7 @@
         <v>45929</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16426,7 +16428,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16499,7 +16501,7 @@
         <v>46136</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16572,7 +16574,7 @@
         <v>45617</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16650,7 +16652,7 @@
         <v>45705</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16723,7 +16725,7 @@
         <v>44840</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16796,7 +16798,7 @@
         <v>45077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16869,7 +16871,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16942,7 +16944,7 @@
         <v>44893</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17015,7 +17017,7 @@
         <v>46154</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17088,7 +17090,7 @@
         <v>44874</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17161,7 +17163,7 @@
         <v>45223</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17234,7 +17236,7 @@
         <v>46154</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17307,7 +17309,7 @@
         <v>44900</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17380,7 +17382,7 @@
         <v>45833</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17453,7 +17455,7 @@
         <v>45110</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17531,7 +17533,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17604,7 +17606,7 @@
         <v>45222</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17677,7 +17679,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17750,7 +17752,7 @@
         <v>46162</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17823,7 +17825,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17896,7 +17898,7 @@
         <v>44901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17969,7 +17971,7 @@
         <v>46163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18042,7 +18044,7 @@
         <v>45516</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18115,7 +18117,7 @@
         <v>44880</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18188,7 +18190,7 @@
         <v>44880</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18261,7 +18263,7 @@
         <v>45833</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18334,7 +18336,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18407,7 +18409,7 @@
         <v>44552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18480,7 +18482,7 @@
         <v>46169</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18553,7 +18555,7 @@
         <v>46169</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18626,7 +18628,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18699,7 +18701,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18772,7 +18774,7 @@
         <v>45274</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18845,7 +18847,7 @@
         <v>45119</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18923,7 +18925,7 @@
         <v>44812</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18996,7 +18998,7 @@
         <v>45457</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19069,7 +19071,7 @@
         <v>45532</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19142,7 +19144,7 @@
         <v>46170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19215,7 +19217,7 @@
         <v>44559</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19288,7 +19290,7 @@
         <v>44595</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19361,7 +19363,7 @@
         <v>45218</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19434,7 +19436,7 @@
         <v>44637</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19507,7 +19509,7 @@
         <v>45028</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19580,7 +19582,7 @@
         <v>46183</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19658,7 +19660,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19731,7 +19733,7 @@
         <v>46188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19804,7 +19806,7 @@
         <v>44978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19877,7 +19879,7 @@
         <v>46188</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19950,7 +19952,7 @@
         <v>45174</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20023,7 +20025,7 @@
         <v>45125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20101,7 +20103,7 @@
         <v>46190</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20174,7 +20176,7 @@
         <v>46195</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20247,7 +20249,7 @@
         <v>45042</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20320,7 +20322,7 @@
         <v>44556</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20393,7 +20395,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20466,7 +20468,7 @@
         <v>45628</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20539,7 +20541,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20612,7 +20614,7 @@
         <v>44645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20685,7 +20687,7 @@
         <v>45506</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20763,7 +20765,7 @@
         <v>44523</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20841,7 +20843,7 @@
         <v>45832</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20914,7 +20916,7 @@
         <v>44636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20987,7 +20989,7 @@
         <v>44606</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21060,7 +21062,7 @@
         <v>45169</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21138,7 +21140,7 @@
         <v>44623</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21216,7 +21218,7 @@
         <v>44658</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21289,7 +21291,7 @@
         <v>46080</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21362,7 +21364,7 @@
         <v>44635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21435,7 +21437,7 @@
         <v>44635</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21508,7 +21510,7 @@
         <v>44610</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21586,7 +21588,7 @@
         <v>46080</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21659,7 +21661,7 @@
         <v>44635</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21732,7 +21734,7 @@
         <v>44708</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21810,7 +21812,7 @@
         <v>45705</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21883,7 +21885,7 @@
         <v>46215</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21961,7 +21963,7 @@
         <v>46215</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22039,7 +22041,7 @@
         <v>46213</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22117,7 +22119,7 @@
         <v>46215</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22195,7 +22197,7 @@
         <v>46215</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22273,7 +22275,7 @@
         <v>46215</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22351,7 +22353,7 @@
         <v>46215</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22429,7 +22431,7 @@
         <v>45180</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22502,7 +22504,7 @@
         <v>44680</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22575,7 +22577,7 @@
         <v>46217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22648,7 +22650,7 @@
         <v>44743</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22721,7 +22723,7 @@
         <v>45153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22794,7 +22796,7 @@
         <v>45219</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22867,7 +22869,7 @@
         <v>44664</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22940,7 +22942,7 @@
         <v>46184</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23013,7 +23015,7 @@
         <v>45219</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23086,7 +23088,7 @@
         <v>44722</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23164,7 +23166,7 @@
         <v>44739</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23237,7 +23239,7 @@
         <v>46154</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23310,7 +23312,7 @@
         <v>45279</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23383,7 +23385,7 @@
         <v>45282</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23456,7 +23458,7 @@
         <v>46265</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23529,7 +23531,7 @@
         <v>45761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23602,7 +23604,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23675,7 +23677,7 @@
         <v>44847</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23748,7 +23750,7 @@
         <v>46066</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23821,7 +23823,7 @@
         <v>44961</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23894,7 +23896,7 @@
         <v>46274</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23967,7 +23969,7 @@
         <v>46274</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24040,7 +24042,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24113,7 +24115,7 @@
         <v>44523</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24191,7 +24193,7 @@
         <v>44671</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24264,7 +24266,7 @@
         <v>45448</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24337,7 +24339,7 @@
         <v>44657</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24410,7 +24412,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24483,7 +24485,7 @@
         <v>44755</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24556,7 +24558,7 @@
         <v>44987</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24629,7 +24631,7 @@
         <v>45019</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24702,7 +24704,7 @@
         <v>44610</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24775,7 +24777,7 @@
         <v>46272</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24848,7 +24850,7 @@
         <v>45443</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24921,7 +24923,7 @@
         <v>45072</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24994,7 +24996,7 @@
         <v>46265</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25067,7 +25069,7 @@
         <v>45553</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25145,7 +25147,7 @@
         <v>45579</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25218,7 +25220,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25296,7 +25298,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25374,7 +25376,7 @@
         <v>44600</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25447,7 +25449,7 @@
         <v>46289</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25520,7 +25522,7 @@
         <v>46289</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25593,7 +25595,7 @@
         <v>45110</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25666,7 +25668,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25744,7 +25746,7 @@
         <v>45603</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25817,7 +25819,7 @@
         <v>44498</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25890,7 +25892,7 @@
         <v>44978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25968,7 +25970,7 @@
         <v>45251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26041,7 +26043,7 @@
         <v>44659</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26114,7 +26116,7 @@
         <v>45281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26187,7 +26189,7 @@
         <v>44574</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26260,7 +26262,7 @@
         <v>45603</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26333,7 +26335,7 @@
         <v>45398</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26406,7 +26408,7 @@
         <v>45110</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26479,7 +26481,7 @@
         <v>45232</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26557,7 +26559,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26635,7 +26637,7 @@
         <v>45019</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26708,7 +26710,7 @@
         <v>45042</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26781,7 +26783,7 @@
         <v>45033</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26854,7 +26856,7 @@
         <v>45370</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26927,7 +26929,7 @@
         <v>45019</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27000,7 +27002,7 @@
         <v>45713</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27073,7 +27075,7 @@
         <v>45638</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27146,7 +27148,7 @@
         <v>45264</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27219,7 +27221,7 @@
         <v>45162</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27292,7 +27294,7 @@
         <v>45378</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27365,7 +27367,7 @@
         <v>43948</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27443,7 +27445,7 @@
         <v>44740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27516,7 +27518,7 @@
         <v>44634</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27594,7 +27596,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27667,7 +27669,7 @@
         <v>46091</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27740,7 +27742,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27813,7 +27815,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22449-2026</t>
+          <t>A 59143-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46155</v>
+        <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2658,17 +2658,22 @@
           <t>VÄSTERÅS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>12.4</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2683,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2692,12 +2697,124 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Järpe
+Tjäder
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59143-2025 artfynd.xlsx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59143-2025 karta.png", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59143-2025 georefererad karta.tif", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59143-2025 FSC-klagomål.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59143-2025 FSC-klagomål mail.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59143-2025 tillsynsbegäran.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59143-2025 tillsynsbegäran mail.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59143-2025 prioriterade fågelarter.docx", "A 59143-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 22449-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Nordfladdermus
 Gråskimlig fladdermus
@@ -2705,112 +2822,112 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 22449-2026 artfynd.xlsx", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 22449-2026 karta.png", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 22449-2026 georefererad karta.tif", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 22449-2026 FSC-klagomål.docx", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 22449-2026 FSC-klagomål mail.docx", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 22449-2026 tillsynsbegäran.docx", "A 22449-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 22449-2026 tillsynsbegäran mail.docx", "A 22449-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 41262-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45174</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>11.4</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>8</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Gulsparv
@@ -2818,116 +2935,116 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 41262-2023 artfynd.xlsx", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 41262-2023 karta.png", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 41262-2023 georefererad karta.tif", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 41262-2023 FSC-klagomål.docx", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 41262-2023 FSC-klagomål mail.docx", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 41262-2023 tillsynsbegäran.docx", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 41262-2023 tillsynsbegäran mail.docx", "A 41262-2023")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 41262-2023 prioriterade fågelarter.docx", "A 41262-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 40782-2022</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>44824</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>3.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>8</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tallticka
@@ -2935,107 +3052,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 40782-2022 artfynd.xlsx", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 40782-2022 karta.png", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 40782-2022 georefererad karta.tif", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 40782-2022 FSC-klagomål.docx", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 40782-2022 FSC-klagomål mail.docx", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 40782-2022 tillsynsbegäran.docx", "A 40782-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 40782-2022 tillsynsbegäran mail.docx", "A 40782-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 47695-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45203</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Svinrot
@@ -3043,107 +3160,107 @@
 Kopparödla</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 47695-2023 artfynd.xlsx", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 47695-2023 karta.png", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 47695-2023 georefererad karta.tif", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 47695-2023 FSC-klagomål.docx", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 47695-2023 FSC-klagomål mail.docx", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 47695-2023 tillsynsbegäran.docx", "A 47695-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 47695-2023 tillsynsbegäran mail.docx", "A 47695-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 47228-2022</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>44852</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>11.6</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>4</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>4</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Vithornad barkskinnbagge
 Xyletinus ater
@@ -3151,111 +3268,111 @@
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 47228-2022 artfynd.xlsx", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 47228-2022 karta.png", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 47228-2022 georefererad karta.tif", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 47228-2022 FSC-klagomål.docx", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 47228-2022 FSC-klagomål mail.docx", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 47228-2022 tillsynsbegäran.docx", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 47228-2022 tillsynsbegäran mail.docx", "A 47228-2022")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 47228-2022 prioriterade fågelarter.docx", "A 47228-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 25672-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>45463</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>11.3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>4</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Flentimotej
@@ -3263,373 +3380,257 @@
 Solvända</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 25672-2024 artfynd.xlsx", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 25672-2024 karta.png", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 25672-2024 georefererad karta.tif", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 25672-2024 FSC-klagomål.docx", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 25672-2024 FSC-klagomål mail.docx", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 25672-2024 tillsynsbegäran.docx", "A 25672-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 25672-2024 tillsynsbegäran mail.docx", "A 25672-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 64201-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45279</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>13</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>3</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>3</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Källpraktmossa
 Stubbspretmossa
 Vanlig rörsvepemossa</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 64201-2023 artfynd.xlsx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 64201-2023 karta.png", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 64201-2023 georefererad karta.tif", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 64201-2023 FSC-klagomål.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 64201-2023 FSC-klagomål mail.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 64201-2023 tillsynsbegäran.docx", "A 64201-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 64201-2023 tillsynsbegäran mail.docx", "A 64201-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 16684-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E27" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>7.9</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>7</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
 Ullticka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 16684-2026 artfynd.xlsx", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 16684-2026 karta.png", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 16684-2026 georefererad karta.tif", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="Z26">
+      <c r="Z27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/knärot/A 16684-2026 karta knärot.png", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 16684-2026 FSC-klagomål.docx", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 16684-2026 FSC-klagomål mail.docx", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 16684-2026 tillsynsbegäran.docx", "A 16684-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 16684-2026 tillsynsbegäran mail.docx", "A 16684-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 59143-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Järpe
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59143-2025 artfynd.xlsx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59143-2025 karta.png", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59143-2025 georefererad karta.tif", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59143-2025 FSC-klagomål.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59143-2025 FSC-klagomål mail.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59143-2025 tillsynsbegäran.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59143-2025 tillsynsbegäran mail.docx", "A 59143-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59143-2025 prioriterade fågelarter.docx", "A 59143-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64735-2023</t>
+          <t>A 59140-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3643,10 +3644,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45281</v>
+        <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3660,23 +3661,23 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3688,826 +3689,827 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Tjäder
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59140-2025 artfynd.xlsx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59140-2025 karta.png", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59140-2025 georefererad karta.tif", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59140-2025 FSC-klagomål.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59140-2025 FSC-klagomål mail.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59140-2025 tillsynsbegäran.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59140-2025 tillsynsbegäran mail.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59140-2025 prioriterade fågelarter.docx", "A 59140-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 64735-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
         <v>6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Vårstarr
 Gullviva</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 64735-2023 artfynd.xlsx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 64735-2023 karta.png", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 64735-2023 georefererad karta.tif", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 64735-2023 FSC-klagomål.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 64735-2023 FSC-klagomål mail.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 64735-2023 tillsynsbegäran.docx", "A 64735-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 64735-2023 tillsynsbegäran mail.docx", "A 64735-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 6249-2024</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>6.5</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Blåsippa
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 6249-2024 artfynd.xlsx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 6249-2024 karta.png", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 6249-2024 georefererad karta.tif", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 6249-2024 FSC-klagomål.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 6249-2024 FSC-klagomål mail.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 6249-2024 tillsynsbegäran.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 6249-2024 tillsynsbegäran mail.docx", "A 6249-2024")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 6249-2024 prioriterade fågelarter.docx", "A 6249-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 14265-2025</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>45740</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>2.1</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>9</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 14265-2025 artfynd.xlsx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 14265-2025 karta.png", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 14265-2025 georefererad karta.tif", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/knärot/A 14265-2025 karta knärot.png", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 14265-2025 FSC-klagomål.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 14265-2025 FSC-klagomål mail.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 14265-2025 tillsynsbegäran.docx", "A 14265-2025")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 14265-2025 tillsynsbegäran mail.docx", "A 14265-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 11804-2022</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>44634</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E32" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>10.6</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Ask
 Svart trolldruva
 Nattviol</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 11804-2022 artfynd.xlsx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 11804-2022 karta.png", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 11804-2022 georefererad karta.tif", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 11804-2022 FSC-klagomål.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 11804-2022 FSC-klagomål mail.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 11804-2022 tillsynsbegäran.docx", "A 11804-2022")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 11804-2022 tillsynsbegäran mail.docx", "A 11804-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>S 4578-2023</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>4.1</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>3</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Vårstarr
 Gullviva</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/S 4578-2023 artfynd.xlsx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/S 4578-2023 karta.png", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/S 4578-2023 georefererad karta.tif", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/S 4578-2023 FSC-klagomål.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/S 4578-2023 FSC-klagomål mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/S 4578-2023 tillsynsbegäran.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/S 4578-2023 tillsynsbegäran mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 17261-2022</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>44678</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1.1</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>2</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Skumticka
 Svartöra</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 17261-2022 artfynd.xlsx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 17261-2022 karta.png", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 17261-2022 georefererad karta.tif", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 17261-2022 FSC-klagomål.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 17261-2022 FSC-klagomål mail.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 17261-2022 tillsynsbegäran.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 17261-2022 tillsynsbegäran mail.docx", "A 17261-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 30759-2022</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>44764</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>0.8</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U35" t="n">
         <v>4</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Blåsippa</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 30759-2022 artfynd.xlsx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 30759-2022 karta.png", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 30759-2022 georefererad karta.tif", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 30759-2022 FSC-klagomål.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 30759-2022 FSC-klagomål mail.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 30759-2022 tillsynsbegäran.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 30759-2022 tillsynsbegäran mail.docx", "A 30759-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 59140-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59140-2025 artfynd.xlsx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59140-2025 karta.png", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59140-2025 georefererad karta.tif", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59140-2025 FSC-klagomål.docx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59140-2025 FSC-klagomål mail.docx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59140-2025 tillsynsbegäran.docx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59140-2025 tillsynsbegäran mail.docx", "A 59140-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/fåglar/A 59140-2025 prioriterade fågelarter.docx", "A 59140-2025")</f>
         <v/>
       </c>
     </row>
@@ -4531,7 +4533,7 @@
         <v>45617</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4642,7 +4644,7 @@
         <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4753,7 +4755,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4859,7 +4861,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4965,7 +4967,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5076,7 +5078,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5191,7 +5193,7 @@
         <v>45942</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5297,7 +5299,7 @@
         <v>44764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5406,7 +5408,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5513,7 @@
         <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5625,7 +5627,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5730,7 +5732,7 @@
         <v>44739</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5835,7 +5837,7 @@
         <v>44641</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5947,7 @@
         <v>44610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6055,7 +6057,7 @@
         <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6160,7 +6162,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6267,7 @@
         <v>45751</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6370,7 +6372,7 @@
         <v>45001</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6475,7 +6477,7 @@
         <v>45692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6580,7 +6582,7 @@
         <v>45645</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6685,7 +6687,7 @@
         <v>45988</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6795,7 +6797,7 @@
         <v>44935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6904,7 +6906,7 @@
         <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7016,7 @@
         <v>44901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7121,7 @@
         <v>46154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7224,7 +7226,7 @@
         <v>46232</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7336,7 @@
         <v>46290</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7448,7 +7450,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7560,7 @@
         <v>45196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7663,7 +7665,7 @@
         <v>45264</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7770,7 @@
         <v>45638</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7873,7 +7875,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7982,7 +7984,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8055,7 +8057,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8128,7 +8130,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8201,7 +8203,7 @@
         <v>44601</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8274,7 +8276,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8347,7 +8349,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8420,7 +8422,7 @@
         <v>44594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8493,7 +8495,7 @@
         <v>44733</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8566,7 +8568,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8644,7 +8646,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8717,7 +8719,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8790,7 +8792,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8863,7 +8865,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8941,7 +8943,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9019,7 +9021,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9097,7 +9099,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9170,7 +9172,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9248,7 +9250,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9321,7 +9323,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9394,7 +9396,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9467,7 +9469,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9540,7 +9542,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9613,7 +9615,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9691,7 +9693,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9764,7 +9766,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9837,7 +9839,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9915,7 +9917,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9993,7 +9995,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10066,7 +10068,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10139,7 +10141,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10212,7 +10214,7 @@
         <v>45180</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10285,7 +10287,7 @@
         <v>45232</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10363,7 +10365,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10436,7 +10438,7 @@
         <v>44637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10509,7 +10511,7 @@
         <v>44739</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10582,7 +10584,7 @@
         <v>44826</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10655,7 +10657,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10728,7 +10730,7 @@
         <v>44559</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10801,7 +10803,7 @@
         <v>45110</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10879,7 +10881,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10957,7 +10959,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11030,7 +11032,7 @@
         <v>45019</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11103,7 +11105,7 @@
         <v>45639</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11176,7 +11178,7 @@
         <v>45887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11249,7 +11251,7 @@
         <v>44961</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11322,7 +11324,7 @@
         <v>44662</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11395,7 +11397,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11468,7 +11470,7 @@
         <v>45595</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11546,7 +11548,7 @@
         <v>45072</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11619,7 +11621,7 @@
         <v>45705</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11692,7 +11694,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11770,7 +11772,7 @@
         <v>45370</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11843,7 +11845,7 @@
         <v>45162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11916,7 +11918,7 @@
         <v>45019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11989,7 +11991,7 @@
         <v>45223</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12062,7 +12064,7 @@
         <v>45908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12135,7 +12137,7 @@
         <v>45908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12208,7 +12210,7 @@
         <v>45628</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12281,7 +12283,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12354,7 +12356,7 @@
         <v>45506</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12432,7 +12434,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12505,7 +12507,7 @@
         <v>45545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12578,7 +12580,7 @@
         <v>45453</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12651,7 +12653,7 @@
         <v>45506</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12729,7 +12731,7 @@
         <v>45798</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12802,7 +12804,7 @@
         <v>44875</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12875,7 +12877,7 @@
         <v>44936</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12948,7 +12950,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13021,7 +13023,7 @@
         <v>45926</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13099,7 +13101,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13172,7 +13174,7 @@
         <v>44987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13245,7 +13247,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13318,7 +13320,7 @@
         <v>44999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13391,7 +13393,7 @@
         <v>45945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13464,7 +13466,7 @@
         <v>45279</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13537,7 +13539,7 @@
         <v>45945</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13610,7 +13612,7 @@
         <v>45235</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13688,7 +13690,7 @@
         <v>45456</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13761,7 +13763,7 @@
         <v>44635</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13834,7 +13836,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13912,7 +13914,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13990,7 +13992,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14063,7 +14065,7 @@
         <v>46084</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14136,7 +14138,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14209,7 +14211,7 @@
         <v>44594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14282,7 +14284,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14355,7 +14357,7 @@
         <v>46078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14428,7 +14430,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14501,7 +14503,7 @@
         <v>46083</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14574,7 +14576,7 @@
         <v>45125</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14652,7 +14654,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14725,7 +14727,7 @@
         <v>45279</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14798,7 +14800,7 @@
         <v>45973</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14871,7 +14873,7 @@
         <v>44816</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14944,7 +14946,7 @@
         <v>46104</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15017,7 +15019,7 @@
         <v>45617</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15095,7 +15097,7 @@
         <v>45979</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15168,7 +15170,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15241,7 +15243,7 @@
         <v>45119</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15319,7 +15321,7 @@
         <v>44645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15392,7 +15394,7 @@
         <v>46112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15465,7 +15467,7 @@
         <v>46112</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15543,7 +15545,7 @@
         <v>46112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15621,7 +15623,7 @@
         <v>46112</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15699,7 +15701,7 @@
         <v>46112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15772,7 +15774,7 @@
         <v>44648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15845,7 +15847,7 @@
         <v>45219</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15918,7 +15920,7 @@
         <v>45988</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15996,7 +15998,7 @@
         <v>46120</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16074,7 +16076,7 @@
         <v>46121</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16152,7 +16154,7 @@
         <v>44635</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16225,7 +16227,7 @@
         <v>44635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16298,7 +16300,7 @@
         <v>45833</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16371,7 +16373,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16444,7 +16446,7 @@
         <v>44908</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16517,7 +16519,7 @@
         <v>45174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16590,7 +16592,7 @@
         <v>45027</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16663,7 +16665,7 @@
         <v>45027</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16736,7 +16738,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16809,7 +16811,7 @@
         <v>45607</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16882,7 +16884,7 @@
         <v>45516</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16955,7 +16957,7 @@
         <v>44999</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17028,7 +17030,7 @@
         <v>44880</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17101,7 +17103,7 @@
         <v>44880</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17174,7 +17176,7 @@
         <v>45833</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17247,7 +17249,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17320,7 +17322,7 @@
         <v>45219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17393,7 +17395,7 @@
         <v>44958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17466,7 +17468,7 @@
         <v>44582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17544,7 +17546,7 @@
         <v>45833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17617,7 +17619,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17690,7 +17692,7 @@
         <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17763,7 +17765,7 @@
         <v>44600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17836,7 +17838,7 @@
         <v>45414</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17909,7 +17911,7 @@
         <v>45042</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17982,7 +17984,7 @@
         <v>45279</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18055,7 +18057,7 @@
         <v>45553</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18133,7 +18135,7 @@
         <v>45160</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18206,7 +18208,7 @@
         <v>44659</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18279,7 +18281,7 @@
         <v>44595</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18352,7 +18354,7 @@
         <v>46154</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18425,7 +18427,7 @@
         <v>46154</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18498,7 +18500,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18571,7 +18573,7 @@
         <v>46162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18644,7 +18646,7 @@
         <v>46163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18717,7 +18719,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18790,7 +18792,7 @@
         <v>46169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18863,7 +18865,7 @@
         <v>46169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18936,7 +18938,7 @@
         <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19009,7 +19011,7 @@
         <v>45077</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19082,7 +19084,7 @@
         <v>45274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19155,7 +19157,7 @@
         <v>46169</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19228,7 +19230,7 @@
         <v>46170</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19301,7 +19303,7 @@
         <v>44914</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19374,7 +19376,7 @@
         <v>45832</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19447,7 +19449,7 @@
         <v>45042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19520,7 +19522,7 @@
         <v>44717</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19593,7 +19595,7 @@
         <v>45219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19666,7 +19668,7 @@
         <v>46183</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19744,7 +19746,7 @@
         <v>46188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19817,7 +19819,7 @@
         <v>46188</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19890,7 +19892,7 @@
         <v>46190</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19963,7 +19965,7 @@
         <v>44680</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20036,7 +20038,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20109,7 +20111,7 @@
         <v>45110</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20182,7 +20184,7 @@
         <v>44636</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20255,7 +20257,7 @@
         <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20328,7 +20330,7 @@
         <v>45628</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20401,7 +20403,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20474,7 +20476,7 @@
         <v>44986</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20547,7 +20549,7 @@
         <v>44899</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20620,7 +20622,7 @@
         <v>45019</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20693,7 +20695,7 @@
         <v>44636</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20771,7 +20773,7 @@
         <v>44636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20849,7 +20851,7 @@
         <v>44840</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20922,7 +20924,7 @@
         <v>44574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20995,7 +20997,7 @@
         <v>44893</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21068,7 +21070,7 @@
         <v>46080</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21141,7 +21143,7 @@
         <v>44664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21214,7 +21216,7 @@
         <v>46080</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21287,7 +21289,7 @@
         <v>46213</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21365,7 +21367,7 @@
         <v>46215</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21443,7 +21445,7 @@
         <v>46215</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21521,7 +21523,7 @@
         <v>46215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21599,7 +21601,7 @@
         <v>46215</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21677,7 +21679,7 @@
         <v>46215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21755,7 +21757,7 @@
         <v>46215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21833,7 +21835,7 @@
         <v>45110</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21906,7 +21908,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21979,7 +21981,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22052,7 +22054,7 @@
         <v>45019</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22125,7 +22127,7 @@
         <v>46217</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22198,7 +22200,7 @@
         <v>45042</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22271,7 +22273,7 @@
         <v>44900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22344,7 +22346,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22417,7 +22419,7 @@
         <v>45761</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22490,7 +22492,7 @@
         <v>46154</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22563,7 +22565,7 @@
         <v>45083</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22636,7 +22638,7 @@
         <v>45400</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22709,7 +22711,7 @@
         <v>44606</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22782,7 +22784,7 @@
         <v>46066</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22855,7 +22857,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22928,7 +22930,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23001,7 +23003,7 @@
         <v>44978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23074,7 +23076,7 @@
         <v>44523</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23152,7 +23154,7 @@
         <v>45532</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23225,7 +23227,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23298,7 +23300,7 @@
         <v>46274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23371,7 +23373,7 @@
         <v>45579</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23444,7 +23446,7 @@
         <v>44874</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23517,7 +23519,7 @@
         <v>44901</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23590,7 +23592,7 @@
         <v>45218</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23663,7 +23665,7 @@
         <v>45264</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23736,7 +23738,7 @@
         <v>45042</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23809,7 +23811,7 @@
         <v>45457</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23882,7 +23884,7 @@
         <v>45553</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23960,7 +23962,7 @@
         <v>46272</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24033,7 +24035,7 @@
         <v>44523</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24111,7 +24113,7 @@
         <v>46265</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24184,7 +24186,7 @@
         <v>46289</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24257,7 +24259,7 @@
         <v>44623</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24335,7 +24337,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24408,7 +24410,7 @@
         <v>45033</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24481,7 +24483,7 @@
         <v>44556</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24554,7 +24556,7 @@
         <v>46290</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24632,7 +24634,7 @@
         <v>44498</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24705,7 +24707,7 @@
         <v>45603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24778,7 +24780,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24856,7 +24858,7 @@
         <v>46290</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24934,7 +24936,7 @@
         <v>44792</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25007,7 +25009,7 @@
         <v>45222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25080,7 +25082,7 @@
         <v>44874</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25153,7 +25155,7 @@
         <v>44708</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25231,7 +25233,7 @@
         <v>44755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25304,7 +25306,7 @@
         <v>44523</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25382,7 +25384,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25460,7 +25462,7 @@
         <v>44482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25533,7 +25535,7 @@
         <v>45705</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25606,7 +25608,7 @@
         <v>46287</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25679,7 +25681,7 @@
         <v>45713</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25752,7 +25754,7 @@
         <v>44658</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25825,7 +25827,7 @@
         <v>44903</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25898,7 +25900,7 @@
         <v>45281</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25971,7 +25973,7 @@
         <v>44978</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26049,7 +26051,7 @@
         <v>45028</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26122,7 +26124,7 @@
         <v>45398</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26195,7 +26197,7 @@
         <v>45603</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26268,7 +26270,7 @@
         <v>45366</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26341,7 +26343,7 @@
         <v>44994</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26414,7 +26416,7 @@
         <v>44537</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26487,7 +26489,7 @@
         <v>44722</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26565,7 +26567,7 @@
         <v>45282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26638,7 +26640,7 @@
         <v>45296</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26711,7 +26713,7 @@
         <v>45037</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26789,7 +26791,7 @@
         <v>45223</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26862,7 +26864,7 @@
         <v>44552</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26935,7 +26937,7 @@
         <v>45153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27008,7 +27010,7 @@
         <v>45448</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27081,7 +27083,7 @@
         <v>44657</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27154,7 +27156,7 @@
         <v>45378</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27227,7 +27229,7 @@
         <v>43948</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27305,7 +27307,7 @@
         <v>44740</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27378,7 +27380,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27451,7 +27453,7 @@
         <v>44634</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27529,7 +27531,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27602,7 +27604,7 @@
         <v>46113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27675,7 +27677,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>46112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46155</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45174</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44824</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>45203</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44852</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45463</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45337</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45740</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>44634</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44678</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>44764</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>45617</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45942</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45232</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44739</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44641</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>44610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45897</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45751</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45001</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45645</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>45988</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>46154</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>46232</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>46290</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45196</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45264</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45638</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44601</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44711</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44733</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45180</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45232</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>44739</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44826</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44559</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45110</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45019</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45639</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44961</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44662</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45595</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45072</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>45705</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>46030</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>45370</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45223</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45908</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45628</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45908</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45506</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45453</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45506</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45798</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44875</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44936</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44977</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45926</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44987</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>44999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>45279</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45945</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45235</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45456</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44635</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45952</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>46084</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44594</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46083</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45125</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45279</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45973</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>44816</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>46104</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45617</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45979</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45119</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>46112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>46112</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>46112</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45219</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45988</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>46120</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46121</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44635</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>44635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45833</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44908</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45027</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45027</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45607</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45516</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44999</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44880</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>44880</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45833</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45219</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>44958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>44582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45833</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>44600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45414</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45042</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45279</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45553</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45160</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44659</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44595</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46154</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>46154</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45761</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>46162</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>46163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45077</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>46169</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46170</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>44914</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45832</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>44717</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>46183</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>46188</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>46190</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44680</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45110</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44636</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45628</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44986</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44899</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45019</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44636</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44840</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44893</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>46080</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>44664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>46080</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46213</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>46215</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>46215</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>46215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>46215</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>46215</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45110</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45019</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46217</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45042</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44900</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45761</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>46154</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45083</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45400</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44606</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>46066</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>46066</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44523</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45532</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45579</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44874</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44901</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45218</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45264</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45042</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45457</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45553</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>46272</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>44523</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46265</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>46289</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44623</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45033</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44556</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>46290</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44498</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>46290</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44792</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44874</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44708</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44523</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45705</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46287</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45713</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44658</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>44903</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45281</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44978</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45028</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45398</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45603</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45366</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44994</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44537</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44722</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45296</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45037</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45223</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44552</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45448</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44657</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45378</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>43948</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>44740</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44634</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>46113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44871</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44523</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44852</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>46112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>46155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45740</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>44634</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45337</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44678</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45617</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>44901</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>45692</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45264</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44641</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45751</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45638</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45196</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45107</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45645</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45001</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45988</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44865</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46154</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46290</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46290</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44525</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44601</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44733</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44691</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44645</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44540</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44676</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>44692</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44662</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44659</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45281</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44893</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44874</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45453</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45400</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44900</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45110</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45279</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45222</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45603</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>45398</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45456</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45296</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45110</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45223</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45232</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45553</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45257</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45414</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44847</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45019</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45042</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45083</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44482</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45033</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44874</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45370</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45019</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44908</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44812</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45457</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45279</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45042</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44559</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45019</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44595</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44899</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45264</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45908</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45908</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45162</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45378</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45908</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45366</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44637</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44914</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45174</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45125</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44636</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45926</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44556</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45506</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45506</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44523</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44636</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>44999</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44717</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44606</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44623</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44658</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44662</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45235</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44635</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44610</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44635</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44509</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45947</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45705</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45639</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45180</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44680</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44958</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45953</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45219</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45833</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45027</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45027</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44999</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45219</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44722</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45607</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>44739</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44582</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45516</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45279</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45019</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45282</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44880</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45833</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45705</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44648</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45979</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44961</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44840</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45832</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44523</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45077</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44671</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45735</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45988</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46112</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46112</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46112</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>46112</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>46112</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>46121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46120</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44657</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44755</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44987</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44610</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45443</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45072</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45553</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44600</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45929</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>46136</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45110</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45603</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>44498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>46030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>46059</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46062</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46154</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45952</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46084</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46083</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44594</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46084</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45761</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>46163</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46169</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45274</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46188</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>46196</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46215</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46215</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46217</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46184</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46154</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46265</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46066</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46274</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46274</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46066</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46272</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46265</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>46290</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46289</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46080</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46215</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46080</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>46303</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46303</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46303</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46303</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46215</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>43948</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44634</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46091</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44871</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44523</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>44601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46155</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>46183</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45174</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>44852</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>46112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>46155</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45740</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>44634</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45337</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44678</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45617</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>46290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>44901</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>45692</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45264</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>44641</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45751</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45638</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45196</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>45107</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45645</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45001</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45988</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44865</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46154</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46290</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46290</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>44525</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44679</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44601</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44733</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44691</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44645</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44540</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44571</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44676</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>44692</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44662</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44659</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45281</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44893</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44874</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45453</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45400</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44900</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45110</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45279</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45222</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45603</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>45398</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45456</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45296</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45110</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45223</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45232</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44816</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45553</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45257</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>45414</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44847</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44903</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45019</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45042</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45083</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44482</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45033</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44874</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45370</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45019</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44908</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44812</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45457</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45279</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>45532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45042</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44559</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45019</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45638</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44595</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44899</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45264</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45908</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45908</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45162</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45378</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45908</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45366</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44637</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44914</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45174</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45125</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44636</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45042</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45926</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44556</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45506</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45506</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44523</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44636</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>44999</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44717</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44606</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44623</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44658</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44662</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45235</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>44635</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44635</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44610</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44635</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44509</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44708</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45947</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45705</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45639</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45180</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44680</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44958</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45953</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45219</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44664</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45833</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45027</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45027</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44999</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45219</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>44722</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45607</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>44739</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44582</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45516</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45279</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45019</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45282</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44880</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44880</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45833</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45761</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45705</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44648</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45979</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45979</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>44961</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44840</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45832</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44523</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45077</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44671</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45448</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45735</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45988</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46112</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46112</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>46112</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>46112</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>46112</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>46121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46120</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44657</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44755</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44987</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44610</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45443</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45072</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45553</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44600</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45929</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>46136</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45110</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45603</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>44498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>46030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>46059</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46062</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46154</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45952</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46084</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>46083</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44594</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>46084</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45761</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>46163</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46169</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>46169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45274</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46170</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46188</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>46188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46190</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>46195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>46196</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46215</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46215</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46217</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46184</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46154</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46265</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46066</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46274</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>46274</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46066</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46272</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46265</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>46290</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46289</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46080</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46215</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46080</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>46303</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46303</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46303</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46303</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46215</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>43948</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>44740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44634</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46091</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>46134</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46155</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44852</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45281</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45337</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45740</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>44634</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4187,24 +4187,24 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S 4578-2023</t>
+          <t>A 39917-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45281</v>
+        <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4218,732 +4218,733 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
       </c>
       <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
         <v>3</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Blodticka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 39917-2026 artfynd.xlsx", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 39917-2026 karta.png", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 39917-2026 georefererad karta.tif", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 39917-2026 FSC-klagomål.docx", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 39917-2026 FSC-klagomål mail.docx", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 39917-2026 tillsynsbegäran.docx", "A 39917-2026")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 39917-2026 tillsynsbegäran mail.docx", "A 39917-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S 4578-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Backsippa
 Vårstarr
 Gullviva</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/S 4578-2023 artfynd.xlsx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/S 4578-2023 karta.png", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/S 4578-2023 georefererad karta.tif", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/S 4578-2023 FSC-klagomål.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/S 4578-2023 FSC-klagomål mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/S 4578-2023 tillsynsbegäran.docx", "S 4578-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/S 4578-2023 tillsynsbegäran mail.docx", "S 4578-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 17261-2022</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>44678</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>1.1</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Skumticka
 Svartöra</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 17261-2022 artfynd.xlsx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 17261-2022 karta.png", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 17261-2022 georefererad karta.tif", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 17261-2022 FSC-klagomål.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 17261-2022 FSC-klagomål mail.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 17261-2022 tillsynsbegäran.docx", "A 17261-2022")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 17261-2022 tillsynsbegäran mail.docx", "A 17261-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 30759-2022</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>44764</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="E36" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>0.8</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>5</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>4</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Blåsippa</t>
         </is>
       </c>
-      <c r="W35">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 30759-2022 artfynd.xlsx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="X35">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 30759-2022 karta.png", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="Y35">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 30759-2022 georefererad karta.tif", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AA35">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 30759-2022 FSC-klagomål.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AB35">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 30759-2022 FSC-klagomål mail.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AC35">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 30759-2022 tillsynsbegäran.docx", "A 30759-2022")</f>
         <v/>
       </c>
-      <c r="AD35">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 30759-2022 tillsynsbegäran mail.docx", "A 30759-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>A 9327-2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>46070</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="E37" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>3.3</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>2</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>2</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>Svart trolldruva
 Tibast</t>
         </is>
       </c>
-      <c r="W36">
+      <c r="W37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 9327-2026 artfynd.xlsx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="X36">
+      <c r="X37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 9327-2026 karta.png", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="Y36">
+      <c r="Y37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 9327-2026 georefererad karta.tif", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AA36">
+      <c r="AA37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 9327-2026 FSC-klagomål.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AB36">
+      <c r="AB37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 9327-2026 FSC-klagomål mail.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 9327-2026 tillsynsbegäran.docx", "A 9327-2026")</f>
         <v/>
       </c>
-      <c r="AD36">
+      <c r="AD37">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 9327-2026 tillsynsbegäran mail.docx", "A 9327-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>A 22452-2026</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>46155</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="E38" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>4</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>2</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>2</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Kopparödla</t>
         </is>
       </c>
-      <c r="W37">
+      <c r="W38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 22452-2026 artfynd.xlsx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="X37">
+      <c r="X38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 22452-2026 karta.png", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="Y37">
+      <c r="Y38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 22452-2026 georefererad karta.tif", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AA37">
+      <c r="AA38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 22452-2026 FSC-klagomål.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AB37">
+      <c r="AB38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 22452-2026 FSC-klagomål mail.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AC37">
+      <c r="AC38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 22452-2026 tillsynsbegäran.docx", "A 22452-2026")</f>
         <v/>
       </c>
-      <c r="AD37">
+      <c r="AD38">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 22452-2026 tillsynsbegäran mail.docx", "A 22452-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>A 59566-2021</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>44491</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+      <c r="E39" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>VÄSTERÅS</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>2.1</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>2</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>4</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Vanlig flatbagge</t>
         </is>
       </c>
-      <c r="W38">
+      <c r="W39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 59566-2021 artfynd.xlsx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="X38">
+      <c r="X39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 59566-2021 karta.png", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 59566-2021 georefererad karta.tif", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 59566-2021 FSC-klagomål.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 59566-2021 FSC-klagomål mail.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 59566-2021 tillsynsbegäran.docx", "A 59566-2021")</f>
         <v/>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 59566-2021 tillsynsbegäran mail.docx", "A 59566-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A 39917-2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>VÄSTERÅS</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>Blodticka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/artfynd/A 39917-2026 artfynd.xlsx", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor/A 39917-2026 karta.png", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/kartor_geotiff/A 39917-2026 georefererad karta.tif", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomål/A 39917-2026 FSC-klagomål.docx", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/klagomålsmail/A 39917-2026 FSC-klagomål mail.docx", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsyn/A 39917-2026 tillsynsbegäran.docx", "A 39917-2026")</f>
-        <v/>
-      </c>
-      <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1980/tillsynsmail/A 39917-2026 tillsynsbegäran mail.docx", "A 39917-2026")</f>
         <v/>
       </c>
     </row>
@@ -4967,7 +4968,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5082,7 +5083,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5192,7 +5193,7 @@
         <v>45617</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5303,7 +5304,7 @@
         <v>45942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,7 +5410,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5518,7 +5519,7 @@
         <v>44607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5623,7 +5624,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5729,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5843,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,7 +5948,7 @@
         <v>44641</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,7 +6058,7 @@
         <v>44610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6167,7 +6168,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6272,7 +6273,7 @@
         <v>45001</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6377,7 +6378,7 @@
         <v>45692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6482,7 +6483,7 @@
         <v>45645</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6587,7 +6588,7 @@
         <v>45897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6692,7 +6693,7 @@
         <v>45751</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6797,7 +6798,7 @@
         <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6908,7 @@
         <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7013,7 @@
         <v>44901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7117,7 +7118,7 @@
         <v>45988</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7227,7 +7228,7 @@
         <v>44935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7337,7 @@
         <v>46232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7447,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7561,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7670,7 +7671,7 @@
         <v>45196</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7776,7 @@
         <v>45264</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7880,7 +7881,7 @@
         <v>45638</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7986,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8094,7 +8095,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8167,7 +8168,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8240,7 +8241,7 @@
         <v>44679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8313,7 +8314,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8386,7 +8387,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8459,7 +8460,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8532,7 +8533,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8606,7 @@
         <v>44711</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8679,7 @@
         <v>44691</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8756,7 +8757,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8829,7 +8830,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8902,7 +8903,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8980,7 +8981,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9058,7 +9059,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9136,7 +9137,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9209,7 +9210,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9287,7 +9288,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9360,7 +9361,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9433,7 +9434,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9506,7 +9507,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9579,7 +9580,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9652,7 +9653,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9730,7 +9731,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9803,7 +9804,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9876,7 +9877,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9954,7 +9955,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10032,7 +10033,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10105,7 +10106,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10178,7 +10179,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10251,7 +10252,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10324,7 +10325,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10397,7 +10398,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10470,7 +10471,7 @@
         <v>45180</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10543,7 +10544,7 @@
         <v>45232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10621,7 +10622,7 @@
         <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10694,7 +10695,7 @@
         <v>44739</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10767,7 +10768,7 @@
         <v>45110</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10845,7 +10846,7 @@
         <v>44559</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10918,7 +10919,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10996,7 +10997,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11069,7 +11070,7 @@
         <v>45639</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11142,7 +11143,7 @@
         <v>44961</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11215,7 +11216,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11288,7 +11289,7 @@
         <v>45072</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11361,7 +11362,7 @@
         <v>45705</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11434,7 +11435,7 @@
         <v>45370</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11507,7 +11508,7 @@
         <v>45162</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11580,7 +11581,7 @@
         <v>45223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11653,7 +11654,7 @@
         <v>45019</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11726,7 +11727,7 @@
         <v>45628</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11799,7 +11800,7 @@
         <v>45638</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11872,7 +11873,7 @@
         <v>45019</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11945,7 +11946,7 @@
         <v>45453</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12018,7 +12019,7 @@
         <v>44875</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12091,7 +12092,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12164,7 +12165,7 @@
         <v>45506</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12242,7 +12243,7 @@
         <v>44977</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12315,7 +12316,7 @@
         <v>44987</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12388,7 +12389,7 @@
         <v>44999</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12461,7 +12462,7 @@
         <v>45279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12534,7 +12535,7 @@
         <v>45456</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12607,7 +12608,7 @@
         <v>44635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12680,7 +12681,7 @@
         <v>45251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12753,7 +12754,7 @@
         <v>44743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12826,7 +12827,7 @@
         <v>45279</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12899,7 +12900,7 @@
         <v>45125</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12977,7 +12978,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13050,7 +13051,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13128,7 +13129,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13201,7 +13202,7 @@
         <v>45887</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13274,7 +13275,7 @@
         <v>44648</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13347,7 +13348,7 @@
         <v>45219</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13420,7 +13421,7 @@
         <v>45929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13493,7 +13494,7 @@
         <v>44635</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13566,7 +13567,7 @@
         <v>44635</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13639,7 +13640,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13712,7 +13713,7 @@
         <v>45595</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13790,7 +13791,7 @@
         <v>46136</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13863,7 +13864,7 @@
         <v>45257</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13936,7 +13937,7 @@
         <v>45908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14009,7 +14010,7 @@
         <v>45908</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14082,7 +14083,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14155,7 +14156,7 @@
         <v>45174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14228,7 +14229,7 @@
         <v>45908</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14301,7 +14302,7 @@
         <v>45027</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14374,7 +14375,7 @@
         <v>45027</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14447,7 +14448,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14520,7 +14521,7 @@
         <v>45607</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14593,7 +14594,7 @@
         <v>44999</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14666,7 +14667,7 @@
         <v>45926</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14744,7 +14745,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14817,7 +14818,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14890,7 +14891,7 @@
         <v>44582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14968,7 +14969,7 @@
         <v>45945</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15041,7 +15042,7 @@
         <v>46154</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15114,7 +15115,7 @@
         <v>44812</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15187,7 +15188,7 @@
         <v>45945</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15260,7 +15261,7 @@
         <v>44600</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15333,7 +15334,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15411,7 +15412,7 @@
         <v>46154</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15484,7 +15485,7 @@
         <v>45953</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15557,7 +15558,7 @@
         <v>45414</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15630,7 +15631,7 @@
         <v>45042</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15703,7 +15704,7 @@
         <v>45279</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15776,7 +15777,7 @@
         <v>45761</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15849,7 +15850,7 @@
         <v>45553</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15927,7 +15928,7 @@
         <v>45973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16000,7 +16001,7 @@
         <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16073,7 +16074,7 @@
         <v>45160</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16146,7 +16147,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16219,7 +16220,7 @@
         <v>45979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16292,7 +16293,7 @@
         <v>44595</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16365,7 +16366,7 @@
         <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16438,7 +16439,7 @@
         <v>46163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16511,7 +16512,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16589,7 +16590,7 @@
         <v>46169</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16662,7 +16663,7 @@
         <v>46169</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16735,7 +16736,7 @@
         <v>46169</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16808,7 +16809,7 @@
         <v>45274</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16881,7 +16882,7 @@
         <v>46169</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16954,7 +16955,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17027,7 +17028,7 @@
         <v>44509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17100,7 +17101,7 @@
         <v>45077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17173,7 +17174,7 @@
         <v>44914</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17246,7 +17247,7 @@
         <v>45042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17319,7 +17320,7 @@
         <v>44717</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17392,7 +17393,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17470,7 +17471,7 @@
         <v>45219</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17543,7 +17544,7 @@
         <v>44680</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17616,7 +17617,7 @@
         <v>45110</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17689,7 +17690,7 @@
         <v>44636</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17762,7 +17763,7 @@
         <v>45628</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17835,7 +17836,7 @@
         <v>46059</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17908,7 +17909,7 @@
         <v>45443</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17981,7 +17982,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18054,7 +18055,7 @@
         <v>44986</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18127,7 +18128,7 @@
         <v>44899</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18200,7 +18201,7 @@
         <v>46183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18278,7 +18279,7 @@
         <v>45019</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18351,7 +18352,7 @@
         <v>46188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18424,7 +18425,7 @@
         <v>46188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18497,7 +18498,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18575,7 +18576,7 @@
         <v>44636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18653,7 +18654,7 @@
         <v>45952</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18731,7 +18732,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18804,7 +18805,7 @@
         <v>44594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18877,7 +18878,7 @@
         <v>46084</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18950,7 +18951,7 @@
         <v>46078</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19023,7 +19024,7 @@
         <v>44840</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19096,7 +19097,7 @@
         <v>44574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19169,7 +19170,7 @@
         <v>46083</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19242,7 +19243,7 @@
         <v>44893</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19315,7 +19316,7 @@
         <v>44664</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19388,7 +19389,7 @@
         <v>46190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19461,7 +19462,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19534,7 +19535,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19607,7 +19608,7 @@
         <v>45110</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19680,7 +19681,7 @@
         <v>45019</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19753,7 +19754,7 @@
         <v>45019</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19826,7 +19827,7 @@
         <v>45042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19899,7 +19900,7 @@
         <v>46195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19972,7 +19973,7 @@
         <v>46112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20045,7 +20046,7 @@
         <v>44900</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20118,7 +20119,7 @@
         <v>46112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20196,7 +20197,7 @@
         <v>46112</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20274,7 +20275,7 @@
         <v>46112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20352,7 +20353,7 @@
         <v>46112</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20425,7 +20426,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20498,7 +20499,7 @@
         <v>45083</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20571,7 +20572,7 @@
         <v>46120</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20649,7 +20650,7 @@
         <v>46121</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20727,7 +20728,7 @@
         <v>45400</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20800,7 +20801,7 @@
         <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20873,7 +20874,7 @@
         <v>45735</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20946,7 +20947,7 @@
         <v>44978</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21019,7 +21020,7 @@
         <v>44523</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21097,7 +21098,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21171,7 @@
         <v>45579</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21243,7 +21244,7 @@
         <v>44874</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21316,7 +21317,7 @@
         <v>44901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21389,7 +21390,7 @@
         <v>45218</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21462,7 +21463,7 @@
         <v>45264</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21535,7 +21536,7 @@
         <v>45042</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21608,7 +21609,7 @@
         <v>45457</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21681,7 +21682,7 @@
         <v>45553</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21759,7 +21760,7 @@
         <v>46215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21837,7 +21838,7 @@
         <v>46215</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21915,7 +21916,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21988,7 +21989,7 @@
         <v>46217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22061,7 +22062,7 @@
         <v>44523</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22139,7 +22140,7 @@
         <v>46154</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22212,7 +22213,7 @@
         <v>44623</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22290,7 +22291,7 @@
         <v>46066</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22363,7 +22364,7 @@
         <v>46066</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22436,7 +22437,7 @@
         <v>45033</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22509,7 +22510,7 @@
         <v>44556</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22582,7 +22583,7 @@
         <v>46274</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22655,7 +22656,7 @@
         <v>46274</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22728,7 +22729,7 @@
         <v>44498</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22801,7 +22802,7 @@
         <v>45603</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22874,7 +22875,7 @@
         <v>44792</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22947,7 +22948,7 @@
         <v>45222</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23020,7 +23021,7 @@
         <v>44874</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23093,7 +23094,7 @@
         <v>44708</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23171,7 +23172,7 @@
         <v>44755</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23244,7 +23245,7 @@
         <v>44523</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23322,7 +23323,7 @@
         <v>45169</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23400,7 +23401,7 @@
         <v>45705</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23473,7 +23474,7 @@
         <v>45713</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23546,7 +23547,7 @@
         <v>44658</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23619,7 +23620,7 @@
         <v>44903</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23692,7 +23693,7 @@
         <v>45281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23765,7 +23766,7 @@
         <v>44978</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23843,7 +23844,7 @@
         <v>45028</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23916,7 +23917,7 @@
         <v>46272</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23989,7 +23990,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24062,7 +24063,7 @@
         <v>45398</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24135,7 +24136,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24208,7 +24209,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24281,7 +24282,7 @@
         <v>45366</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24354,7 +24355,7 @@
         <v>44994</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24427,7 +24428,7 @@
         <v>44537</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24500,7 +24501,7 @@
         <v>44722</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24578,7 +24579,7 @@
         <v>46290</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24656,7 +24657,7 @@
         <v>45282</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24729,7 +24730,7 @@
         <v>45296</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24802,7 +24803,7 @@
         <v>45037</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24880,7 +24881,7 @@
         <v>45223</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24953,7 +24954,7 @@
         <v>46290</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25031,7 +25032,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25109,7 +25110,7 @@
         <v>44552</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25182,7 +25183,7 @@
         <v>45153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25255,7 +25256,7 @@
         <v>45448</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25328,7 +25329,7 @@
         <v>44657</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25401,7 +25402,7 @@
         <v>46287</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25474,7 +25475,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25547,7 +25548,7 @@
         <v>45378</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25620,7 +25621,7 @@
         <v>46080</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25693,7 +25694,7 @@
         <v>46215</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25771,7 +25772,7 @@
         <v>46303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25844,7 +25845,7 @@
         <v>46215</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25922,7 +25923,7 @@
         <v>46303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25995,7 +25996,7 @@
         <v>46303</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26068,7 +26069,7 @@
         <v>46303</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26141,7 +26142,7 @@
         <v>45506</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26219,7 +26220,7 @@
         <v>45545</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26292,7 +26293,7 @@
         <v>45798</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26365,7 +26366,7 @@
         <v>46215</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26443,7 +26444,7 @@
         <v>46265</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26516,7 +26517,7 @@
         <v>45235</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26594,7 +26595,7 @@
         <v>45603</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26667,7 +26668,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26745,7 +26746,7 @@
         <v>45833</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26818,7 +26819,7 @@
         <v>45516</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26891,7 +26892,7 @@
         <v>44880</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26964,7 +26965,7 @@
         <v>44880</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27037,7 +27038,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27110,7 +27111,7 @@
         <v>45833</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27183,7 +27184,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27256,7 +27257,7 @@
         <v>43948</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27334,7 +27335,7 @@
         <v>44740</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27407,7 +27408,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27480,7 +27481,7 @@
         <v>44634</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27558,7 +27559,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27631,7 +27632,7 @@
         <v>46113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27704,7 +27705,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46155</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>46183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>44601</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46155</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44852</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45463</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45281</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45337</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45740</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>44634</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44678</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46070</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>46155</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46290</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45617</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>45232</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44641</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44610</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45001</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45692</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45645</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45751</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46154</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>44901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45988</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>46232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>46290</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>46290</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45196</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45264</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45638</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44711</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44691</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44540</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44880</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44722</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44571</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44676</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44572</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44623</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44761</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44847</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44847</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45180</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44739</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45110</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44559</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45639</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44961</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45072</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45705</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45370</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45162</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>45223</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45019</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>45628</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45638</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>45019</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45453</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>44875</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45506</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44977</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44987</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44999</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>45279</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>45456</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>44635</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>44743</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45279</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45125</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45119</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44645</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45887</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>44648</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45219</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44635</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>44635</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45595</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>46136</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45257</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45908</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45174</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45908</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45027</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45027</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45607</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>44999</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45926</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45945</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>46154</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44812</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45945</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>44600</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46154</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45953</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45414</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45042</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45279</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45761</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45553</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>46162</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45160</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>44595</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>46169</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>46169</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>46169</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45274</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46169</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44509</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>44914</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>44717</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45219</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>44680</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45110</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44636</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45628</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>46059</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45443</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44986</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44899</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>46183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45019</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46188</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45952</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44594</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>46084</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>46078</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44840</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>46083</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44893</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44664</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>46190</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45110</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45019</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45019</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44900</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>46112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46112</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>46112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46112</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45083</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46120</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>46121</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45400</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44606</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45735</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44978</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44523</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>45532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45579</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44874</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44901</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45218</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45264</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45042</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45457</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45553</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>46215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>46215</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>46217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44523</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>46154</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>44623</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>46066</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>46066</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45033</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44556</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46274</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>46274</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44498</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45603</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44792</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45222</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44874</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44708</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>44755</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>44523</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45169</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45705</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45713</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44658</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>44903</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45281</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44978</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45028</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46272</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45398</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45603</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45366</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44994</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44537</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44722</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>46290</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45282</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45296</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45037</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45223</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>46290</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44552</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45448</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44657</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46287</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45378</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>46080</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>46215</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>46215</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46303</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46303</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45506</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45545</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45798</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46215</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>46265</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45235</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>45603</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45833</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45516</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>44880</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44880</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45833</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45833</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>43948</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44740</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>44634</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>46113</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>46134</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46183</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45463</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46155</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44824</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45337</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44634</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>46290</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45740</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44678</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45617</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>46155</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45942</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45751</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45692</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45264</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>46290</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>46290</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44641</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44935</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>46154</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45645</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45001</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45638</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44540</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44636</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44692</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44880</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44722</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44571</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44676</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44662</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44572</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44623</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44761</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45072</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45553</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44825</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44792</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45414</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45110</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45603</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45908</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44498</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45761</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>46162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>46163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46169</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>46169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>46169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45274</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44659</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45453</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45400</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45456</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44574</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45296</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45223</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45603</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45398</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>46183</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45110</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>46188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44847</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46190</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>46195</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45019</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45033</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>46196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>44903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45370</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45979</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45083</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45019</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45988</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45638</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>46215</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46215</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>46217</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45264</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45162</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45378</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44874</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46066</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46066</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45019</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>44908</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45545</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45506</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>46290</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46290</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>46289</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45235</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45279</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45603</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>46062</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46287</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46084</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>46083</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46078</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>46084</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45833</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>46215</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46080</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45516</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>46104</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44880</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44880</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44875</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46112</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>46112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>46303</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46303</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46303</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>46121</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46120</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>46303</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44994</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46265</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45832</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44899</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>46215</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45366</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45929</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44914</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46136</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44936</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>44636</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44636</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46272</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46274</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46274</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45037</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44999</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44977</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44717</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44662</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46154</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46154</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44509</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45639</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45027</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45027</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44826</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>44999</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44582</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45705</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44840</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45077</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44893</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>44874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44900</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45110</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45279</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45222</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45257</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44901</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44812</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45457</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45532</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44559</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45218</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44637</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45028</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45160</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45125</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44556</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45628</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44552</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44645</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45506</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44523</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44636</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44623</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44658</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44635</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44635</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44635</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44708</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45705</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45180</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44680</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45153</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45219</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44664</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45219</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44722</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>44739</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45761</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44648</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44847</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44961</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44523</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>44671</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45448</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44657</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44755</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44987</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45019</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45443</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>43948</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44740</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44634</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>46091</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>46113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>46134</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt VÄSTERÅS.xlsx
+++ b/Översikt VÄSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44684</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45548</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>46118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44523</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44871</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>44523</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45261</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>46029</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44607</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>46183</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46155</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46126</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45463</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46155</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>44824</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44852</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45337</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>44634</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>46290</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45740</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45281</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44678</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45617</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>46155</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45942</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>44764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45751</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45692</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45264</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>46290</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>46290</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44641</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44935</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>46154</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>45645</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>45001</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45638</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45219</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>44628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44601</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44594</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44691</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44540</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44636</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44692</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44880</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44551</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>44722</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44571</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44676</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44662</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44572</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44645</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44623</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44761</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45072</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45887</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45553</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44825</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44792</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45414</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45110</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45603</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45908</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44498</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45761</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>46162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45908</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>46163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46169</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>46169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>46169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45274</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45251</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44659</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45453</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45400</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45456</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44574</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45296</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45223</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>44816</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45603</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45398</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>46183</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45110</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>46188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>44847</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46190</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>46195</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45019</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45033</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>46196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>44903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45370</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45979</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45083</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45019</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45988</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45638</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>46215</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46215</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>46217</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45264</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45162</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45378</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44874</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46066</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46066</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45019</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>44908</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45545</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45506</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>46290</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46290</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>46289</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45235</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45279</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45603</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>46062</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46287</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46084</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>46083</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46078</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>46084</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45833</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>46215</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46080</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45516</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>46104</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44880</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44880</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44875</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>44537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>46112</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>46112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>46112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>46303</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46303</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46303</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>46121</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>46120</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>46303</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44994</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46265</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45832</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44899</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>46215</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45366</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45929</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44914</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46136</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44936</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>44636</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44636</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46272</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46274</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>46274</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45037</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44999</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44977</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44717</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44662</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>46154</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46154</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44509</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45639</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45027</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45027</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44826</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>44999</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44582</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45019</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45705</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44840</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45077</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44893</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>44874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45223</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>44900</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45110</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45279</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45222</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45257</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44901</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44812</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45457</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45532</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44559</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>44595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45218</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44637</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45028</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45160</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>44978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45125</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44556</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45628</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>44552</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44645</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45506</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>44523</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44636</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44606</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44623</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>44658</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44635</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44635</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44635</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44708</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45705</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45180</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44680</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44743</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45153</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45219</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44664</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45219</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>44722</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>44739</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45761</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44648</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>44847</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44961</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44523</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>44671</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45448</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44657</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44755</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44987</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45019</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45443</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>43948</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44740</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44634</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45005</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>46091</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>46113</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>46134</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
